--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
@@ -1286,14 +1286,14 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>**同日、令和8年度交付金の該当状況調査票集計表（市町村分）と評価指標を受領し、小野町の得点を項目ごとに整理した。****これまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（令和5年度の取組の評価）のものであり、2年の間に得点は大きく変わっていた。**合計は233点（令和6年度）→324点（令和7年度）→**537点（令和8年度）**で、**全国平均454.8点を82点上回り、全国258位／1,536、県内13位／59である。****介護給付適正化は弱点ではなく強みだった。**主要3事業はいずれも実施されており、医療情報との突合は全保険者の上位1割。0点はケアプラン点検の実施割合（配点16点）だけである。**体制・取組68点（配点満点）は第9期計画の記載に支えられており、第10期計画に同じ水準の記載を置かなければ失点する。****最大の弱点は在宅医療・在宅介護連携（支援Ⅲ）で55点・県内39位。8つの目標のうち全国平均を下回るのはここだけであり、評価指標が求める4つの場面ごとの目指すべき姿を計画に書けば動く。**</t>
+          <t>**同日、令和8年度交付金の該当状況調査票集計表（市町村分）と評価指標を受領し、小野町の得点を項目ごとに整理した。****これまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（令和5年度の取組の評価）のものであり、2年の間に得点は大きく変わっていた。**合計は233点（令和6年度）→324点（令和7年度）→**537点（令和8年度）**で、**市町村分の平均454.8点を82点上回り、市町村分1,536のうち258位、県内13位／59である。****受領したのは市町村分のみで、公表順位の母数は広域連合を含む1,741保険者。258位は公表順位ではない。****介護給付適正化は弱点ではなく強みだった。**医療情報との突合は全保険者の上位1割で、0点はケアプラン点検の実施割合（配点16点）だけである。**ただし主要3事業の「実施」は該当状況調査に対する町の回答（予定を含む）で、内容は確かめられていない。また体制・取組68点の根拠となっている文書も確認できていない（第9期計画本文には評価指標の記載がない）。****最大の弱点は在宅医療・在宅介護連携（支援Ⅲ）で55点・県内39位。8つの目標のうち全国平均を下回るのはここだけであり、評価指標が求める4つの場面ごとの目指すべき姿を計画に書けば動く。**</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>**成果品は、素案が第6版（84表・図3点）、協議会資料が第2版（49表・図9点）に達した。**素案には「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。**あわせて打合せ資料一式（次第・現在地と論点・決定依頼事項一覧・打合せ記録）を作成した。決めていただくこと11件、いただきたい資料13件である。****ここから先は当方の作業ではなく町の意思決定が律速になる。**</t>
+          <t>**成果品は、素案が第6版（84表・図3点）、協議会資料が第2版（49表・図9点）に達した。**素案には「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。**あわせて打合せ資料一式（次第・現在地と論点・決定依頼事項一覧・打合せ記録）を作成した。決めていただくこと11件、いただきたい資料15件である。****ここから先は当方の作業ではなく町の意思決定が律速になる。**</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>**打合せ資料一式を作成（決定11件・依頼資料13件）**</t>
+          <t>**打合せ資料一式を作成（決定11件・依頼資料15件）**</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
-          <t>**工程変更協議資料と確認事項12件を作成済み（うち高齢者に係るもの8件）。****9月28日に打合せ資料一式（19_打合せ・次第／現在地と論点／決定依頼事項一覧／打合せ記録の4点）を作成した。**決めていただくこと11件、いただきたい資料13件、配布資料15件を90分の次第に落とし込んでいる。仕様書8①により打合せ記録は受託者が作成し町と相互に確認する</t>
+          <t>**工程変更協議資料と確認事項12件を作成済み（うち高齢者に係るもの8件）。****9月28日に打合せ資料一式（19_打合せ・次第／現在地と論点／決定依頼事項一覧／打合せ記録の4点）を作成した。**決めていただくこと11件、いただきたい資料15件、配布資料15件を90分の次第に落とし込んでいる。仕様書8①により打合せ記録は受託者が作成し町と相互に確認する</t>
         </is>
       </c>
       <c r="O9" s="16" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>**9月28日に市町村分の集計表と評価指標を受領し、小野町の得点を項目ごとに整理した（21_給付適正化・交付金／取りまとめ9章・22表・図4点）。****令和8年度交付金は537点／800点で全国平均454.8点を82点上回り、全国258位／1,536・県内13位／59である。****介護給付適正化（推進Ⅱ）は84点で全国平均を上回る強みであり、体制・取組68点は配点満点。主要3事業はいずれも実施されており、医療情報との突合は全保険者の上位1割。0点はケアプラン点検の実施割合（配点16点）だけである。****8つの目標のうち全国平均を下回るのは支援Ⅲ（在宅医療・在宅介護連携）のみで、55点・県内39位。評価指標が求める4つの場面ごとの目指すべき姿が設定されていないことによる。****素案 第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。****なお、それまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（233点）のものであり、2年前の状況だった。**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理している（08_協議会資料）。福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）</t>
+          <t>**9月28日に市町村分の集計表と評価指標を受領し、小野町の得点を項目ごとに整理した（21_給付適正化・交付金／取りまとめ9章・22表・図4点）。****令和8年度交付金は537点／800点で市町村分の平均454.8点を82点上回り、市町村分1,536のうち258位・県内13位／59である。****ただし受領したのは市町村分のみで、公表順位の母数は広域連合を含む1,741保険者。258位は公表順位ではない**（令和7年度は表内1,339位に対し公表1,513位）。**介護給付適正化（推進Ⅱ）は84点で平均を上回る強みであり、体制・取組68点は配点満点。医療情報との突合は全保険者の上位1割。0点はケアプラン点検の実施割合（配点16点）だけである。****主要3事業の「実施」は該当状況調査に対する町の回答（予定を含む）であり、実施の内容は確かめられていない。****また体制・取組68点の根拠となっている文書が確認できていない。第9期計画本文には主要3事業の記載はあるが、評価指標も毎年度の定量的な目標も書かれていない。****8つの目標のうち全国平均を下回るのは支援Ⅲ（在宅医療・在宅介護連携）のみで、55点・県内39位。評価指標が求める4つの場面ごとの目指すべき姿が設定されていないことによる。****素案 第4章 基本目標2に「⑦ 在宅医療・介護連携の推進」を新設し、基本目標3① の適正化の記述を実際の得点に合わせて訂正した。****なお、それまで用いていた見える化システムの値（W126〜W137）は令和6年度交付金（233点）のものであり、2年前の状況だった。**9月25日に令和8年度の評価指標と全国集計（都道府県分）を受領し、協議会資料として整理している（08_協議会資料）。福島県は令和7年度468点・42位から令和8年度530点・26位へ上がり、伸び幅＋62点は47都道府県で3位。ただし全国平均535.6点に届かず、東北6県では5番目。**全国の6割以上が得点していて福島県が0点の項目が21件あり、うち認知症施策に関する市町村支援（全国の93.6％が得点）、チームオレンジ設置状況（70.2％）、介護予防等と保健事業の一体的実施に向けた環境整備ウ・エ・オ（80〜83％）は小野町の施策に直に効く。****県の支援が薄い領域として、素案は町が自前で組み立てる前提で書く。****令和8年度に成果指向型配分枠（100点・800点とは別枠）が新設され、対象層の特定とアウトプット／アウトカム指標の分離、目標値の記載を求めている。第4章の成果指標42件のうち38件が目標値未設定であり、整理の仕方が交付金の配分に直に効く。**評価結果は計画本文には載せず毎年度の協議会資料として扱う（評価結果を外部の議論の場で検証すること自体が指標の要件であるため）</t>
         </is>
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>**令和6年度のケアプラン点検の実施件数（0点の理由の特定）と、令和8年度の該当状況調査票の控え（体制・取組で得点した項目の根拠資料）**</t>
+          <t>**①令和6年度のケアプラン点検の実施件数（0点の理由の特定）②令和8年度の該当状況調査票の控え（体制・取組で得点した項目の根拠資料）③介護給付費適正化方策とその評価指標を定めた文書（指標1イ・8点の根拠）④広域連合分の集計表（公表順位の母数での位置）**</t>
         </is>
       </c>
       <c r="P20" s="21" t="n"/>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
-          <t>**9月28日に受領した令和8年度交付金の該当状況調査票集計表（市町村分）により、主要3事業の実施状況が確かめられた（21_給付適正化・交付金・9章・22表・図4点）。****3事業とも実施しており、縦覧点検4帳票の全件点検と医療情報との突合は配点満点（突合の実施割合は全保険者の上位1割）。0点はケアプラン点検の実施割合（配点16点）だけである。****目標Ⅱ（介護給付適正化）は84点で全国平均69.1点を上回り、体制・取組68点は配点満点。これは第9期計画に適正化方策と評価指標が書かれていることに支えられており、第10期計画に同じ水準の記載を置かなければ失点する。**位置づけは案A（独立した節）・案B（施策の中）・案C（別冊）の3案を示し、**当方は案Bをお勧めし、素案にはその形で9指標の定量目標を置いた**</t>
+          <t>**9月28日に受領した令和8年度交付金の該当状況調査票集計表（市町村分）により、主要3事業の実施状況が確かめられた（21_給付適正化・交付金・9章・22表・図4点）。****調査票の回答では3事業とも実施しており、縦覧点検4帳票の全件点検と医療情報との突合は配点満点（突合の実施割合は全保険者の上位1割）。0点はケアプラン点検の実施割合（配点16点）だけである。****目標Ⅱ（介護給付適正化）は84点で市町村分の平均69.1点を上回り、体制・取組68点は配点満点。****ただし第9期計画本文（87頁）には主要3事業の記載はあるものの、指標1イが求める「取組の効果を検証するための評価指標」も毎年度の定量的な目標も書かれておらず、32点の根拠が確認できていない。**位置づけは案A（独立した節）・案B（施策の中）・案C（別冊）の3案を示し、**当方は案Bをお勧めし、素案にはその形で9指標の定量目標を置いた**</t>
         </is>
       </c>
       <c r="O52" s="16" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>**町との打合せ（保険料の決定・決定11件・依頼資料13件）**</t>
+          <t>**町との打合せ（保険料の決定・決定11件・依頼資料15件）**</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>**1,574保険者×1,563列。小野町537点／800点、全国258位／1,536、県内13位／59。介護給付適正化の主要3事業の実施状況が確かめられた。見える化の値（W126〜W137）は令和6年度交付金のものだった**</t>
+          <t>**1,574保険者×1,563列。小野町537点／800点、市町村分1,536のうち258位、県内13位／59。介護給付適正化の主要3事業について町の回答（実施）が確かめられた。見える化の値（W126〜W137）は令和6年度交付金のものだった。****広域連合分は別表であり未受領。公表順位の母数は1,741保険者**</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>残項目を再依頼する（打合せの依頼資料13件）。とくに地域支援事業費の内訳は総合事業・通いの場の評価に必須</t>
+          <t>残項目を再依頼する（打合せの依頼資料15件）。とくに地域支援事業費の内訳は総合事業・通いの場の評価に必須</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>**介護給付適正化計画の位置づけが未決**</t>
+          <t>**介護給付適正化計画の位置づけが未決／評価指標の根拠が不明**</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>**介護保険法117条5項は市町村介護給付適正化計画を定めることを求めているが、第9期計画はその名称では置いていない**</t>
+          <t>**介護保険法117条5項は市町村介護給付適正化計画を定めることを求めているが、第9期計画はその名称では置いていない。また第9期計画本文には主要3事業の記載はあるものの、交付金の指標1イが求める評価指標の記載がない**</t>
         </is>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>**指針が求める事業ごとの毎年度の定量的な目標を、どこに書くかが決まらない**</t>
+          <t>**指針が求める事業ごとの毎年度の定量的な目標を、どこに書くかが決まらない。また現に8点を得ている指標1イの根拠が確かめられず、次の評価で落ちる可能性がある**</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -12182,29 +12182,59 @@
     </row>
     <row r="18">
       <c r="A18" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>**交付金の順位は市町村分の中での順位にすぎない**</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>**受領した集計表は市町村分のみ（1,536保険者）で、広域連合分は別表。同表の令和7年度の順位欄は1〜1,741位まであり、上位100位のうち83しか本表に現れない**</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>**当方が算出した「全国258位」は公表順位ではない。令和7年度は本表の中で1,339位に対し公表1,513位で、174位の差がある。成果品に載せる順位は母数を明記しないと誤解を招く**</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>**成果品の記載を「市町村分◯位／1,536」に統一した。広域連合分の集計表を町に照会する（依頼資料15）**</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>**在宅医療・介護連携の目指すべき姿が設定されていない**</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>**令和8年度交付金の支援Ⅲは55点・県内39位。8つの目標のうち全国平均を下回るのはここだけである**</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>**評価指標が求める4つの場面ごとの目指すべき姿がないことによるもので、5項目・25点を落としている（全国では半数以上が得点している）**</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>**素案 第4章 基本目標2⑦ に案を置いた。公立小野町地方綜合病院・田村郡医師会等との調整のうえ確定する（決定11）**</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
@@ -1223,7 +1223,7 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>令和7年度調査の結果は集計結果・分析報告書として取りまとめ、素案第2版に反映した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の92.9％が需要側の要因で、供給制約は0.6％であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替えた。</t>
+          <t>令和7年度調査の結果は集計結果・分析報告書として取りまとめ、素案第2版に反映した。**在宅の要介護認定者の42.1％がサービスを利用しておらず、その理由の上位3つはいずれも需要側のもので、供給側の理由を挙げた方は各1人（0.6％）であった。**これにより第10期の施策方向を、供給確保から認定運用の確認・利用意向への働きかけ・レスパイトへ組み替えた。</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>**同日、国の「（改修版）総合事業の充実に向けたワークシート」を受領した。****本町が訪問型サービスB・通所型サービスB（住民主体）を実施していることが分かった。**これまで実施の有無が確認できていなかったものである。**生産年齢人口は令和2年の4,677人から令和32年の2,399人へ半減する一方、認定者数は788人から808人と横ばいで、2030年に▲122人、2040年に▲345人の供給不足が生じる。**第10期の期間中はなお需要に追いつくこと、本町の見込量が在宅の利用と利用回（日）数を増やしていないためこの制約と整合することを確かめた。**見込量そのものは変えていない。**</t>
+          <t>**同日、国の「（改修版）総合事業の充実に向けたワークシート」を受領した。****本町に訪問型サービスB・通所型サービスB（住民主体）の担い手が各1団体あることが分かった。**これまで確認できていなかったものである（ただし令和4年度以降の実施の有無は無回答で、令和5年度の通所型Bの利用者数は0人。現在の実施状況は未確認）。**生産年齢人口は令和2年の4,677人から令和32年の2,399人へ半減する一方、認定者数は788人から808人と横ばいで、2030年に▲122人、2040年に▲345人の供給不足が生じる。**第10期の期間中はなお需要に追いつくこと、本町の見込量が在宅の利用と利用回（日）数を増やしていないためこの制約と整合することを確かめた。**見込量そのものは変えていない。**</t>
         </is>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>**サービスBの実施と、主要3事業の実施状況が確かめられた**</t>
+          <t>**サービスBの担い手と、主要3事業についての町の回答が確かめられた**</t>
         </is>
       </c>
       <c r="E69" s="9" t="n"/>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="N8" s="16" t="inlineStr">
         <is>
-          <t>**9月8日に介護保険事業状況報告（年報）令和3〜7年度（各47様式）、国保連合会業務統計表（月報）28か月分、第10期将来推計用推計人口を受領。**依頼票のN1・S1〜S5が解決し、S7は令和6年度分のみ解決。**9月28日に、国の「（改修版）総合事業の充実に向けたワークシート」と令和8年度交付金の該当状況調査票集計表（市町村分）・評価指標を受領した。**前者で訪問型サービスB・通所型サービスBの実施が、後者で介護給付適正化の主要3事業の実施状況が確かめられた</t>
+          <t>**9月8日に介護保険事業状況報告（年報）令和3〜7年度（各47様式）、国保連合会業務統計表（月報）28か月分、第10期将来推計用推計人口を受領。**依頼票のN1・S1〜S5が解決し、S7は令和6年度分のみ解決。**9月28日に、国の「（改修版）総合事業の充実に向けたワークシート」と令和8年度交付金の該当状況調査票集計表（市町村分）・評価指標を受領した。**前者で訪問型サービスB・通所型サービスBの担い手が各1団体あることが、後者で介護給付適正化の主要3事業の実施状況が確かめられた</t>
         </is>
       </c>
       <c r="O8" s="16" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="N15" s="16" t="inlineStr">
         <is>
-          <t>**見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録。**9月28日に受領した国の（改修版）総合事業ワークシートにより、本町が訪問型サービスB・通所型サービスB（住民主体）を実施していることが分かった（訪問型A・通所型Aは実施していない）。**これまで実施の有無が確認できていなかったものである</t>
+          <t>**見える化は通いの場がR2まで、総合事業はR1・R2のみで値もほぼ空。**F7〜F14は本町の値が未登録。**9月28日に受領した国の（改修版）総合事業ワークシートにより、本町に訪問型サービスB・通所型サービスB（住民主体）の担い手が各1団体あることが分かった（訪問型A・通所型Aは実施していない）。**国の実施状況調査で令和元年度〜令和3年度に「実施の有無＝有」と回答され、市町村内の事業所数は平成29年度から令和4年度まで各1で一貫している。**ただし令和4年度以降の実施の有無は無回答で、令和5年度の利用者数は訪問型B 24人・通所型B 0人である**</t>
         </is>
       </c>
       <c r="O15" s="16" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="N21" s="16" t="inlineStr">
         <is>
-          <t>**9月28日に受領した国の「（改修版）総合事業の充実に向けたワークシート」と説明書を1行ずつ読み、確認結果を取りまとめた（20_総合事業ワークシート・18表・図3点）。****分かったことが3つある。**①**本町は訪問型サービスB・通所型サービスB（住民主体）を実施している（訪問型A・通所型Aは実施していない）。**これまで実施の有無が確認できていなかった。②**生産年齢人口は令和2年の4,677人から令和32年の2,399人へ半減する一方、認定者数は788人から808人と横ばいで、認定者1人を支える生産年齢人口は5.9人から3.0人になる。**2030年に▲122人、2040年に▲345人の供給不足が生じる。第10期の期間中はなお持つが、直後から効く。③**本町の見込量は在宅の利用と利用回（日）数を増やしていないため、この制約と整合する。見込量そのものを変える必要はない。****素案 第4章④に「人材の供給制約からみた見込量の妥当性」として反映した**</t>
+          <t>**9月28日に受領した国の「（改修版）総合事業の充実に向けたワークシート」と説明書を1行ずつ読み、確認結果を取りまとめた（20_総合事業ワークシート・18表・図3点）。****分かったことが3つある。**①**本町に訪問型サービスB・通所型サービスB（住民主体）の担い手が各1団体ある（訪問型A・通所型Aは実施していない）。****ただし実施の有無の回答は令和3年度が最後で、令和5年度の通所型Bの利用者数は0人である。現在の実施状況は未確認。**②**生産年齢人口は令和2年の4,677人から令和32年の2,399人へ半減する一方、認定者数は788人から808人と横ばいで、認定者1人を支える生産年齢人口は5.9人から3.0人になる。**2030年に▲122人、2040年に▲345人の供給不足が生じる。第10期の期間中はなお持つが、直後から効く。③**本町の見込量は在宅の利用と利用回（日）数を増やしていないため、この制約と整合する。見込量そのものを変える必要はない。****素案 第4章④に「人材の供給制約からみた見込量の妥当性」として反映した**</t>
         </is>
       </c>
       <c r="O21" s="16" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="P46" s="17" t="inlineStr">
         <is>
-          <t>**残る114箇所の内訳は、協議会で設定する目標値54、町データ待ち42、町・国の決定12、見える化出力6。****受託者の算定によるものは残っていない**（第6版で新設した⑦在宅医療・介護連携と適正化の目標により、協議会で設定するものと町データ待ちのものが増えている）。町データ待ちの筆頭は成果指標の現状値、一般介護予防事業費・包括的支援事業・任意事業費の事業別内訳、地域支援事業の量（13事業）、認知症対応型共同生活介護の増床の経緯**</t>
+          <t>**残る115箇所の内訳は、協議会で設定する目標値54、町データ待ち43、町・国の決定12、見える化出力6。****受託者の算定によるものは残っていない**（第6版で新設した⑦在宅医療・介護連携と適正化の目標により、協議会で設定するものと町データ待ちのものが増えている）。町データ待ちの筆頭は成果指標の現状値、一般介護予防事業費・包括的支援事業・任意事業費の事業別内訳、地域支援事業の量（13事業）、認知症対応型共同生活介護の増床の経緯**</t>
         </is>
       </c>
       <c r="Q46" s="21" t="n"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
-          <t>**残るのは成果指標の目標値（協議会で設定54）と町データ待ち42。**とくに成果指標の現状値17項目が入らないと目標値を置けない</t>
+          <t>**残るのは成果指標の目標値（協議会で設定54）と町データ待ち43。**とくに成果指標の現状値17項目が入らないと目標値を置けない</t>
         </is>
       </c>
       <c r="P49" s="21" t="n"/>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>**5章＋資料編・84表・図3点。未確定114箇所を4区分で明示（協議会で設定54／町データ待ち42／決定後に記載12／見える化出力待ち6）。受託者が算定すべき箇所は0件**</t>
+          <t>**5章＋資料編・84表・図3点。未確定115箇所を4区分で明示（協議会で設定54／町データ待ち43／決定後に記載12／見える化出力待ち6）。受託者が算定すべき箇所は0件**</t>
         </is>
       </c>
       <c r="H5" s="16" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>**サービスBの実施と主要3事業の実施状況が確かめられた**</t>
+          <t>**サービスBの担い手と、主要3事業についての町の回答が確かめられた**</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>**将来推計人口、調整済み軽度認定率、総合事業の実施状況調査の回答、上限額の算式。訪問型サービスB・通所型サービスBの実施が判明した**</t>
+          <t>**将来推計人口、調整済み軽度認定率、総合事業の実施状況調査の回答、上限額の算式。訪問型サービスB・通所型サービスBの担い手が各1団体あることが判明した（現在も実施しているかは未確認）**</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>未利用理由の92.9％が需要側（供給制約は0.6％）。供給確保ではなく認定運用の確認・利用意向への働きかけ・レスパイトで対応する</t>
+          <t>未利用理由の上位3つは需要側（供給側は各1人・0.6％）。供給確保ではなく認定運用の確認・利用意向への働きかけ・レスパイトで対応する</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
@@ -12251,7 +12251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12296,21 +12296,21 @@
     </row>
     <row r="2">
       <c r="A2" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>給付適正化</t>
+          <t>集計値の検証</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>**交付金の分析の基礎データを、地域包括ケア「見える化」システムの値（令和6年度交付金）から、受領した令和8年度交付金の該当状況調査票集計表（市町村分）に切り替えた。****得点は233点から537点へ変わり、「介護給付適正化が最大の弱点」という整理は「適正化は強みで、弱点は在宅医療・在宅介護連携」に改まった**</t>
+          <t>**成果品に直書きしている集計値を、一次資料から計算し直して突き合わせる点検を導入した（174件）。****令和7年度調査の未利用理由で、複数回答の割合を足し上げていた（92.9％）ことが分かったのを受けたもの**</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>仕様書4(1)①オ</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E2" s="18" t="inlineStr">
@@ -12320,27 +12320,27 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>**21_給付適正化・交付金 の取りまとめに、出所と切替の理由を明記した。令和6年度の値に基づく整理は本書をもって差し替える**</t>
+          <t>**第1号被保険者1人あたり給付月額の県内順位を23位・30位から28位・33位に訂正し、認定率の「県内2位」に年度（令和7年3月末）を付した。見える化の定員の年度も令和7年度から令和6年度に直した**</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>保険料算定</t>
+          <t>給付適正化</t>
         </is>
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>**調整交付金見込額の基数を、標準給付費のみから（標準給付費＋総合事業費）に訂正した。**調整交付金相当額（5％）と同じ基数である</t>
+          <t>**交付金の分析の基礎データを、地域包括ケア「見える化」システムの値（令和6年度交付金）から、受領した令和8年度交付金の該当状況調査票集計表（市町村分）に切り替えた。****得点は233点から537点へ変わり、「介護給付適正化が最大の弱点」という整理は「適正化は強みで、弱点は在宅医療・在宅介護連携」に改まった**</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>仕様書4(2)</t>
+          <t>仕様書4(1)①オ</t>
         </is>
       </c>
       <c r="E3" s="18" t="inlineStr">
@@ -12350,57 +12350,57 @@
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>**見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。町にはまだお出ししていない段階での訂正である**</t>
+          <t>**21_給付適正化・交付金 の取りまとめに、出所と切替の理由を明記した。令和6年度の値に基づく整理は本書をもって差し替える**</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>工程</t>
+          <t>保険料算定</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>高齢者計画の仕様書には工程表がない（工程が定められているのは障がい計画のみ）。業務期間は令和9年3月31日まで</t>
+          <t>**調整交付金見込額の基数を、標準給付費のみから（標準給付費＋総合事業費）に訂正した。**調整交付金相当額（5％）と同じ基数である</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>仕様書3</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>仕様書4(2)</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>**業務期間から逆算した工程案を作成済み。町との合意が未**</t>
+          <t>**見える化システムの出力と1円まで照合し、第9期の実数でも検算した（誤差0.3％）。訂正による差は月額47円で、保険料基準額は6,048円（切上げ6,100円）である。町にはまだお出ししていない段階での訂正である**</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>協議会</t>
+          <t>工程</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>開催回数の指定がない。受託者案は4回</t>
+          <t>高齢者計画の仕様書には工程表がない（工程が定められているのは障がい計画のみ）。業務期間は令和9年3月31日まで</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>仕様書4(5)</t>
+          <t>仕様書3</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -12410,109 +12410,139 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>未</t>
+          <t>**業務期間から逆算した工程案を作成済み。町との合意が未**</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>保険料算定</t>
+          <t>協議会</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>ケース設定を引継ぎ時点の3ケース（基金の扱いのみ）からC1〜C6に組み直した。仕様書が例示する施設整備・制度改正に対応させた</t>
+          <t>開催回数の指定がない。受託者案は4回</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>仕様書4(2)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>仕様書4(5)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>受託者の内部判断。町への説明が必要</t>
+          <t>未</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>認知症計画</t>
+          <t>保険料算定</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>包含の形式（独立章方式／分散＋対応表方式）</t>
+          <t>ケース設定を引継ぎ時点の3ケース（基金の扱いのみ）からC1〜C6に組み直した。仕様書が例示する施設整備・制度改正に対応させた</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>仕様書2(3)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>仕様書4(2)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>**分散＋対応表方式を提案。町の意思決定が未**</t>
+          <t>受託者の内部判断。町への説明が必要</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>認知症計画</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>包含の形式（独立章方式／分散＋対応表方式）</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>仕様書2(3)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>**分散＋対応表方式を提案。町の意思決定が未**</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>打合せ記録</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>契約後の打合せ記録が引継ぎ資料に含まれていない</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>仕様書8①（受託者が作成し相互確認）</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>要対応</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>**様式を作成済み。8月の協議から適用する**</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>※ 仕様書8①により、打合せ記録は受託者が作成し町と相互に確認する。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>※ 仕様書8①により、打合せ記録は受託者が作成し町と相互に確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>※ 様式は 02_キックオフ・業務計画/小野町_工程変更協議資料 の第5節。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_高齢者_20260928.xlsx
@@ -6786,7 +6786,7 @@
       </c>
       <c r="P40" s="17" t="inlineStr">
         <is>
-          <t>**9月15日に、推計方法そのものをバックテストで検証した（推計方法のバックテスト・04_算定・見込量）。**令和5年度・令和6年度を起点に1〜2年先を予測し、実績との絶対誤差を給付費で加重して比べた。総給付費の誤差は、当方の方式（利用率・分母＝第1号被保険者数・窓3年）が3.31％で最も小さい。窓2年3.54％、分母を75歳以上とすると4.24％、直近年度の据え置き5.26％、全サービス一律の伸び5.28％、**大雪地区広域連合の手引きの偏り補正（φ0.5・上限±3％）は5.39％で一律に劣る。**同手引きの判定基準「一律より良いことを示せなければ補正しない」により採らない。分母を認定者数とすると6.39％で、起点年度によって2.20％〜9.60％と振れ幅が大きい</t>
+          <t>**9月15日に、推計方法そのものをバックテストで検証した（推計方法のバックテスト・04_算定・見込量）。**令和5年度・令和6年度を起点に1〜2年先を予測し、実績との絶対誤差を給付費で加重して比べた。総給付費の誤差は、当方の方式（利用率・分母＝第1号被保険者数・窓3年）が3.31％で最も小さい。窓2年3.54％、分母を75歳以上とすると4.24％、直近年度の据え置き5.26％、全サービス一律の伸び5.28％、**他団体の手引きの偏り補正（φ0.5・上限±3％）は5.39％で一律に劣る。**同手引きの判定基準「一律より良いことを示せなければ補正しない」により採らない。分母を認定者数とすると6.39％で、起点年度によって2.20％〜9.60％と振れ幅が大きい</t>
         </is>
       </c>
       <c r="Q40" s="17" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
-          <t>**川崎町の方式（基準年度の要介護度別給付費に要介護度別の認定者数の伸びを乗じる）を小野町のデータで測った。**断層をまたがない令和5年度→令和6年度では誤差▲1.06％と全方式のなかで最も当たる一方、令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。**令和6年度→令和7年度の認定者数は要介護4が0.755倍・要介護5が0.626倍で、給付費の実績が7.4％しか下がっていないのと合わない。**断層の原因が確認できるまでは採らない。解消すれば要介護度の構成の変化を織り込める点で当方より優れる可能性がある</t>
+          <t>**他町村の案件①の方式（基準年度の要介護度別給付費に要介護度別の認定者数の伸びを乗じる）を小野町のデータで測った。**断層をまたがない令和5年度→令和6年度では誤差▲1.06％と全方式のなかで最も当たる一方、令和7年度を予測先に置く2通りでは▲14.66％・▲13.47％となり、3通りの平均では50設定中49位に落ちる。**令和6年度→令和7年度の認定者数は要介護4が0.755倍・要介護5が0.626倍で、給付費の実績が7.4％しか下がっていないのと合わない。**断層の原因が確認できるまでは採らない。解消すれば要介護度の構成の変化を織り込める点で当方より優れる可能性がある</t>
         </is>
       </c>
       <c r="S40" s="17" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>**9月28日に入力が完了し、推計が通った（見える化 推計が通りました／システムとの突合。11_見える化出力依頼）。****施策反映のワーニングはすべて「該当無し」、負の値もなくなった。**残る33件は小野町に利用がないサービスが0のまま延びたもので、直す必要はない。**システムによる保険料基準額は月額6,533円（100円未満切上げ6,600円）で、本計画の6,048円（同6,100円）と485円の差がある。差のほとんどは令和8年度の置き方の違いによるもので、算式そのものは一致する（段階ごとに突き合わせて確認した）。****川崎町・金ケ崎町の両ブランチを確認し、入力時の設定と落とし穴を整理した（見込量算定の方針と不足資料・04_算定・見込量）。**①介護保険事業状況報告の設定で令和8年度のチェックを外す（外さないと令和8年5月の1か月が年度として扱われる）②伸びは令和6年度→令和7年度（完結年度どうし）③1人1月あたり給付費は令和7年度④**施策反映の3画面は編集せず通過する。**編集するとセルがピンクになり「自然体推計に全て戻す」が押せる状態になる。**この状態のまま総括表を出すと、伸びの窓を変えても見込量が動かない**</t>
+          <t>**9月28日に入力が完了し、推計が通った（見える化 推計が通りました／システムとの突合。11_見える化出力依頼）。****施策反映のワーニングはすべて「該当無し」、負の値もなくなった。**残る33件は小野町に利用がないサービスが0のまま延びたもので、直す必要はない。**システムによる保険料基準額は月額6,533円（100円未満切上げ6,600円）で、本計画の6,048円（同6,100円）と485円の差がある。差のほとんどは令和8年度の置き方の違いによるもので、算式そのものは一致する（段階ごとに突き合わせて確認した）。****他町村の案件2件を確認し、入力時の設定と落とし穴を整理した（見込量算定の方針と不足資料・04_算定・見込量）。**①介護保険事業状況報告の設定で令和8年度のチェックを外す（外さないと令和8年5月の1か月が年度として扱われる）②伸びは令和6年度→令和7年度（完結年度どうし）③1人1月あたり給付費は令和7年度④**施策反映の3画面は編集せず通過する。**編集するとセルがピンクになり「自然体推計に全て戻す」が押せる状態になる。**この状態のまま総括表を出すと、伸びの窓を変えても見込量が動かない**</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案。**9月16日に認知症基本法の条文により市町村計画の根拠を第13条第1項（努力義務）、調和規定を第2項、策定手続（意見聴取・公表・評価・5年ごとの検討）を第3項が準用する第12条第3〜7項と確定し、素案に反映した（認知症基本法への対応の点検・03_計画素案）。****施策の柱を認知症施策推進大綱の5本柱から法の基本的施策（第14〜21条）に組み替え、大綱では落ちていた若年性認知症・移動のための交通手段の確保・消費生活被害の防止・孤立の防止を追加した。**北塩原村の法定記載事項チェックと川崎町の骨子案を参照している</t>
+          <t>計画策定業務設計書 第1章（02_キックオフ・業務計画）。分散＋対応表方式を提案。**9月16日に認知症基本法の条文により市町村計画の根拠を第13条第1項（努力義務）、調和規定を第2項、策定手続（意見聴取・公表・評価・5年ごとの検討）を第3項が準用する第12条第3〜7項と確定し、素案に反映した（認知症基本法への対応の点検・03_計画素案）。****施策の柱を認知症施策推進大綱の5本柱から法の基本的施策（第14〜21条）に組み替え、大綱では落ちていた若年性認知症・移動のための交通手段の確保・消費生活被害の防止・孤立の防止を追加した。**他町村の案件の法定記載事項チェックと他町村の案件①の骨子案を参照している</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr">
